--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127225118</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>127225068</v>
       </c>
       <c r="B8" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>127225125</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>127225091</v>
       </c>
       <c r="B10" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127225084</v>
       </c>
       <c r="B11" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>127225123</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127225120</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225074</v>
+        <v>127225113</v>
       </c>
       <c r="B15" t="n">
-        <v>78342</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800820</v>
+        <v>800817</v>
       </c>
       <c r="R15" t="n">
-        <v>7404131</v>
+        <v>7404104</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225113</v>
+        <v>127225122</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800817</v>
+        <v>800973</v>
       </c>
       <c r="R16" t="n">
-        <v>7404104</v>
+        <v>7403839</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225122</v>
+        <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>78373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800973</v>
+        <v>800820</v>
       </c>
       <c r="R17" t="n">
-        <v>7403839</v>
+        <v>7404131</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2276,7 +2276,7 @@
         <v>127225127</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>127225116</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127225118</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>127225068</v>
       </c>
       <c r="B8" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>127225125</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>127225091</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127225084</v>
       </c>
       <c r="B11" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>127225123</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127225120</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127225113</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>127225122</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>78373</v>
+        <v>78376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127225127</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>127225116</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225113</v>
+        <v>127225074</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>78376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800817</v>
+        <v>800820</v>
       </c>
       <c r="R15" t="n">
-        <v>7404104</v>
+        <v>7404131</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225122</v>
+        <v>127225113</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800973</v>
+        <v>800817</v>
       </c>
       <c r="R16" t="n">
-        <v>7403839</v>
+        <v>7404104</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225074</v>
+        <v>127225122</v>
       </c>
       <c r="B17" t="n">
-        <v>78376</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800820</v>
+        <v>800973</v>
       </c>
       <c r="R17" t="n">
-        <v>7404131</v>
+        <v>7403839</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1691,7 +1691,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225123</v>
+        <v>127225120</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801084</v>
+        <v>800870</v>
       </c>
       <c r="R12" t="n">
-        <v>7403880</v>
+        <v>7404019</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225120</v>
+        <v>127225123</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800870</v>
+        <v>801084</v>
       </c>
       <c r="R13" t="n">
-        <v>7404019</v>
+        <v>7403880</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225074</v>
+        <v>127225113</v>
       </c>
       <c r="B15" t="n">
-        <v>78376</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800820</v>
+        <v>800817</v>
       </c>
       <c r="R15" t="n">
-        <v>7404131</v>
+        <v>7404104</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225113</v>
+        <v>127225122</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800817</v>
+        <v>800973</v>
       </c>
       <c r="R16" t="n">
-        <v>7404104</v>
+        <v>7403839</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225122</v>
+        <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>78376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800973</v>
+        <v>800820</v>
       </c>
       <c r="R17" t="n">
-        <v>7403839</v>
+        <v>7404131</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127225084</v>
       </c>
       <c r="B11" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225120</v>
+        <v>127225123</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800870</v>
+        <v>801084</v>
       </c>
       <c r="R12" t="n">
-        <v>7404019</v>
+        <v>7403880</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225123</v>
+        <v>127225120</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801084</v>
+        <v>800870</v>
       </c>
       <c r="R13" t="n">
-        <v>7403880</v>
+        <v>7404019</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,324 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127415031</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91322</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>801052</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7403867</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127415026</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>800601</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7404205</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127415028</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>800688</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7404145</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1497,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127225091</v>
+        <v>127225084</v>
       </c>
       <c r="B10" t="n">
-        <v>80153</v>
+        <v>97327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800756</v>
+        <v>800818</v>
       </c>
       <c r="R10" t="n">
-        <v>7404083</v>
+        <v>7403953</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127225084</v>
+        <v>127225091</v>
       </c>
       <c r="B11" t="n">
-        <v>97327</v>
+        <v>80153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800818</v>
+        <v>800756</v>
       </c>
       <c r="R11" t="n">
-        <v>7403953</v>
+        <v>7404083</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127225118</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>127225068</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>127225125</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127225084</v>
+        <v>127225091</v>
       </c>
       <c r="B10" t="n">
-        <v>97327</v>
+        <v>80157</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800818</v>
+        <v>800756</v>
       </c>
       <c r="R10" t="n">
-        <v>7403953</v>
+        <v>7404083</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127225091</v>
+        <v>127225084</v>
       </c>
       <c r="B11" t="n">
-        <v>80153</v>
+        <v>97331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800756</v>
+        <v>800818</v>
       </c>
       <c r="R11" t="n">
-        <v>7404083</v>
+        <v>7403953</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225123</v>
+        <v>127225120</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801084</v>
+        <v>800870</v>
       </c>
       <c r="R12" t="n">
-        <v>7403880</v>
+        <v>7404019</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225120</v>
+        <v>127225123</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800870</v>
+        <v>801084</v>
       </c>
       <c r="R13" t="n">
-        <v>7404019</v>
+        <v>7403880</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127225113</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2079,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225122</v>
+        <v>127225074</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>78380</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800973</v>
+        <v>800820</v>
       </c>
       <c r="R16" t="n">
-        <v>7403839</v>
+        <v>7404131</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225074</v>
+        <v>127225122</v>
       </c>
       <c r="B17" t="n">
-        <v>78376</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800820</v>
+        <v>800973</v>
       </c>
       <c r="R17" t="n">
-        <v>7404131</v>
+        <v>7403839</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2276,7 +2276,7 @@
         <v>127225127</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>127225116</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>127225105</v>
       </c>
       <c r="B21" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127415031</v>
       </c>
       <c r="B22" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127415026</v>
       </c>
       <c r="B23" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>127415028</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1691,7 +1691,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225120</v>
+        <v>127225123</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800870</v>
+        <v>801084</v>
       </c>
       <c r="R12" t="n">
-        <v>7404019</v>
+        <v>7403880</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225123</v>
+        <v>127225120</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801084</v>
+        <v>800870</v>
       </c>
       <c r="R13" t="n">
-        <v>7403880</v>
+        <v>7404019</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2079,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225074</v>
+        <v>127225122</v>
       </c>
       <c r="B16" t="n">
-        <v>78380</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800820</v>
+        <v>800973</v>
       </c>
       <c r="R16" t="n">
-        <v>7404131</v>
+        <v>7403839</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225122</v>
+        <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>78380</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800973</v>
+        <v>800820</v>
       </c>
       <c r="R17" t="n">
-        <v>7403839</v>
+        <v>7404131</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1691,7 +1691,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225123</v>
+        <v>127225120</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801084</v>
+        <v>800870</v>
       </c>
       <c r="R12" t="n">
-        <v>7403880</v>
+        <v>7404019</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225120</v>
+        <v>127225123</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800870</v>
+        <v>801084</v>
       </c>
       <c r="R13" t="n">
-        <v>7404019</v>
+        <v>7403880</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225113</v>
+        <v>127225074</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>78380</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800817</v>
+        <v>800820</v>
       </c>
       <c r="R15" t="n">
-        <v>7404104</v>
+        <v>7404131</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225074</v>
+        <v>127225113</v>
       </c>
       <c r="B17" t="n">
-        <v>78380</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800820</v>
+        <v>800817</v>
       </c>
       <c r="R17" t="n">
-        <v>7404131</v>
+        <v>7404104</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225074</v>
+        <v>127225122</v>
       </c>
       <c r="B15" t="n">
-        <v>78380</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800820</v>
+        <v>800973</v>
       </c>
       <c r="R15" t="n">
-        <v>7404131</v>
+        <v>7403839</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225122</v>
+        <v>127225113</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800973</v>
+        <v>800817</v>
       </c>
       <c r="R16" t="n">
-        <v>7403839</v>
+        <v>7404104</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225113</v>
+        <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>78380</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800817</v>
+        <v>800820</v>
       </c>
       <c r="R17" t="n">
-        <v>7404104</v>
+        <v>7404131</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127225118</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>127225068</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>127225125</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>127225091</v>
       </c>
       <c r="B10" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127225084</v>
       </c>
       <c r="B11" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>127225120</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127225123</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225122</v>
+        <v>127225113</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800973</v>
+        <v>800817</v>
       </c>
       <c r="R15" t="n">
-        <v>7403839</v>
+        <v>7404104</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2079,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225113</v>
+        <v>127225074</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>78382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800817</v>
+        <v>800820</v>
       </c>
       <c r="R16" t="n">
-        <v>7404104</v>
+        <v>7404131</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225074</v>
+        <v>127225122</v>
       </c>
       <c r="B17" t="n">
-        <v>78380</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800820</v>
+        <v>800973</v>
       </c>
       <c r="R17" t="n">
-        <v>7404131</v>
+        <v>7403839</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2276,7 +2276,7 @@
         <v>127225127</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>127225116</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>127225105</v>
       </c>
       <c r="B21" t="n">
-        <v>56844</v>
+        <v>56846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127415031</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127415026</v>
       </c>
       <c r="B23" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>127415028</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2976,6 +2976,112 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127735578</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>800851</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7404179</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1691,7 +1691,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225120</v>
+        <v>127225123</v>
       </c>
       <c r="B12" t="n">
         <v>79020</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800870</v>
+        <v>801084</v>
       </c>
       <c r="R12" t="n">
-        <v>7404019</v>
+        <v>7403880</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225123</v>
+        <v>127225120</v>
       </c>
       <c r="B13" t="n">
         <v>79020</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801084</v>
+        <v>800870</v>
       </c>
       <c r="R13" t="n">
-        <v>7403880</v>
+        <v>7404019</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2079,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225074</v>
+        <v>127225122</v>
       </c>
       <c r="B16" t="n">
-        <v>78382</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800820</v>
+        <v>800973</v>
       </c>
       <c r="R16" t="n">
-        <v>7404131</v>
+        <v>7403839</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225122</v>
+        <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>78382</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800973</v>
+        <v>800820</v>
       </c>
       <c r="R17" t="n">
-        <v>7403839</v>
+        <v>7404131</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127225091</v>
+        <v>127225084</v>
       </c>
       <c r="B10" t="n">
-        <v>80159</v>
+        <v>97339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800756</v>
+        <v>800818</v>
       </c>
       <c r="R10" t="n">
-        <v>7404083</v>
+        <v>7403953</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127225084</v>
+        <v>127225091</v>
       </c>
       <c r="B11" t="n">
-        <v>97333</v>
+        <v>80159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800818</v>
+        <v>800756</v>
       </c>
       <c r="R11" t="n">
-        <v>7403953</v>
+        <v>7404083</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127415031</v>
       </c>
       <c r="B22" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127415026</v>
       </c>
       <c r="B23" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>127735578</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127225118</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>127225068</v>
       </c>
       <c r="B8" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>127225125</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>127225084</v>
       </c>
       <c r="B10" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127225091</v>
       </c>
       <c r="B11" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>127225123</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127225120</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127225113</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>127225122</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>78382</v>
+        <v>78385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127225127</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>127225116</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>127225105</v>
       </c>
       <c r="B21" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127415031</v>
       </c>
       <c r="B22" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127415026</v>
       </c>
       <c r="B23" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>127415028</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>127735578</v>
       </c>
       <c r="B25" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127225118</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>127225068</v>
       </c>
       <c r="B8" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>127225125</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127225084</v>
+        <v>127225091</v>
       </c>
       <c r="B10" t="n">
-        <v>97342</v>
+        <v>80168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800818</v>
+        <v>800756</v>
       </c>
       <c r="R10" t="n">
-        <v>7403953</v>
+        <v>7404083</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127225091</v>
+        <v>127225084</v>
       </c>
       <c r="B11" t="n">
-        <v>80162</v>
+        <v>97350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800756</v>
+        <v>800818</v>
       </c>
       <c r="R11" t="n">
-        <v>7404083</v>
+        <v>7403953</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225123</v>
+        <v>127225120</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801084</v>
+        <v>800870</v>
       </c>
       <c r="R12" t="n">
-        <v>7403880</v>
+        <v>7404019</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225120</v>
+        <v>127225123</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800870</v>
+        <v>801084</v>
       </c>
       <c r="R13" t="n">
-        <v>7404019</v>
+        <v>7403880</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225113</v>
+        <v>127225122</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800817</v>
+        <v>800973</v>
       </c>
       <c r="R15" t="n">
-        <v>7404104</v>
+        <v>7403839</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2079,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225122</v>
+        <v>127225074</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>78391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800973</v>
+        <v>800820</v>
       </c>
       <c r="R16" t="n">
-        <v>7403839</v>
+        <v>7404131</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225074</v>
+        <v>127225113</v>
       </c>
       <c r="B17" t="n">
-        <v>78385</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800820</v>
+        <v>800817</v>
       </c>
       <c r="R17" t="n">
-        <v>7404131</v>
+        <v>7404104</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2276,7 +2276,7 @@
         <v>127225127</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>127225116</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>127225105</v>
       </c>
       <c r="B21" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127415031</v>
       </c>
       <c r="B22" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127415026</v>
       </c>
       <c r="B23" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>127415028</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>127735578</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127225084</v>
       </c>
       <c r="B11" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127225120</v>
+        <v>127225123</v>
       </c>
       <c r="B12" t="n">
         <v>79029</v>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800870</v>
+        <v>801084</v>
       </c>
       <c r="R12" t="n">
-        <v>7404019</v>
+        <v>7403880</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225123</v>
+        <v>127225120</v>
       </c>
       <c r="B13" t="n">
         <v>79029</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801084</v>
+        <v>800870</v>
       </c>
       <c r="R13" t="n">
-        <v>7403880</v>
+        <v>7404019</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225122</v>
+        <v>127225113</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800973</v>
+        <v>800817</v>
       </c>
       <c r="R15" t="n">
-        <v>7403839</v>
+        <v>7404104</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2079,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225074</v>
+        <v>127225122</v>
       </c>
       <c r="B16" t="n">
-        <v>78391</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800820</v>
+        <v>800973</v>
       </c>
       <c r="R16" t="n">
-        <v>7404131</v>
+        <v>7403839</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,32 +2176,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225113</v>
+        <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>78391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800817</v>
+        <v>800820</v>
       </c>
       <c r="R17" t="n">
-        <v>7404104</v>
+        <v>7404131</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2470,7 +2470,7 @@
         <v>127225087</v>
       </c>
       <c r="B20" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>127415031</v>
       </c>
       <c r="B22" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127415026</v>
       </c>
       <c r="B23" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>127735578</v>
       </c>
       <c r="B25" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -2664,7 +2664,7 @@
         <v>127415031</v>
       </c>
       <c r="B22" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127415026</v>
       </c>
       <c r="B23" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>127735578</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -2664,7 +2664,7 @@
         <v>127415031</v>
       </c>
       <c r="B22" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127415026</v>
       </c>
       <c r="B23" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>127735578</v>
       </c>
       <c r="B25" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -2982,7 +2982,7 @@
         <v>127735578</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 36485-2025 artfynd.xlsx
+++ b/artfynd/A 36485-2025 artfynd.xlsx
@@ -2982,7 +2982,7 @@
         <v>127735578</v>
       </c>
       <c r="B25" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
